--- a/ExperimentsRecord.xlsx
+++ b/ExperimentsRecord.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\TerahertzCode\Terahertz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DC7F1D-4B8A-4246-8C2C-AB83F12132E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05804BA4-DF4E-4AB5-8B33-410C3A2CA16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22500" yWindow="3000" windowWidth="21030" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22845" yWindow="3870" windowWidth="21030" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
   <si>
     <t>名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,10 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pixel size / ONN pixel =&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>150um / 5*5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,7 +192,73 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>training</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>168/168</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pixel size / ONN pixel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 random ONN, w/ 4F</t>
+  </si>
+  <si>
+    <t>250um / 3*3</t>
+  </si>
+  <si>
+    <t>4,6,6,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restormer_ONN8LBlock_v2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testing有問題</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33.6981/33.6979(local)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restormer_ONN8LBlock_v3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restormer_8LBlock_v2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o ONN, w/ 4F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>size設定錯誤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restormer_ONN8LBlock_v4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60/168</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restormer_8LBlock_v3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pull from server</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>167/168</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,11 +614,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="4" width="41.28515625" customWidth="1"/>
+    <col min="2" max="3" width="41.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
     <col min="5" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" customWidth="1"/>
@@ -564,6 +628,7 @@
     <col min="10" max="10" width="16.5703125" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="21.28515625" customWidth="1"/>
+    <col min="17" max="17" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
@@ -606,7 +671,7 @@
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
       <c r="S1" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T1" s="6"/>
       <c r="U1" s="6"/>
@@ -618,7 +683,7 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -677,7 +742,7 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>49152</v>
@@ -733,7 +798,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -782,11 +847,14 @@
       <c r="A7" t="s">
         <v>19</v>
       </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -829,11 +897,14 @@
       <c r="A8" t="s">
         <v>31</v>
       </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>49152</v>
@@ -874,25 +945,28 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9">
         <v>49152</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -901,7 +975,7 @@
         <v>1727518</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N9">
         <v>300000</v>
@@ -917,6 +991,253 @@
       </c>
       <c r="R9">
         <v>0.98750000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>49152</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <v>802711</v>
+      </c>
+      <c r="M10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10">
+        <v>300000</v>
+      </c>
+      <c r="O10" t="s">
+        <v>42</v>
+      </c>
+      <c r="P10">
+        <v>4.2700000000000002E-4</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>49</v>
+      </c>
+      <c r="R10">
+        <v>0.98760000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11">
+        <v>49152</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>807004</v>
+      </c>
+      <c r="M11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11">
+        <v>300000</v>
+      </c>
+      <c r="O11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11">
+        <v>4.26E-4</v>
+      </c>
+      <c r="Q11">
+        <v>33.7027</v>
+      </c>
+      <c r="R11">
+        <v>0.98770000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13">
+        <v>49152</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13">
+        <v>8</v>
+      </c>
+      <c r="I13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>802711</v>
+      </c>
+      <c r="M13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13">
+        <v>300000</v>
+      </c>
+      <c r="O13" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13">
+        <v>3.9300000000000001E-4</v>
+      </c>
+      <c r="Q13">
+        <v>34.057499999999997</v>
+      </c>
+      <c r="R13">
+        <v>0.99129999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14">
+        <v>8</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>802711</v>
+      </c>
+      <c r="M14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14">
+        <v>300000</v>
+      </c>
+      <c r="O14" t="s">
+        <v>55</v>
+      </c>
+      <c r="P14">
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="Q14">
+        <v>25.1998</v>
+      </c>
+      <c r="R14">
+        <v>0.95920000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>802711</v>
+      </c>
+      <c r="M15" t="s">
+        <v>39</v>
+      </c>
+      <c r="N15">
+        <v>300000</v>
+      </c>
+      <c r="O15" t="s">
+        <v>58</v>
+      </c>
+      <c r="P15">
+        <v>3.0019999999999999E-3</v>
+      </c>
+      <c r="Q15">
+        <v>25.2255</v>
+      </c>
+      <c r="R15">
+        <v>0.95940000000000003</v>
       </c>
     </row>
   </sheetData>
